--- a/r5-core-64-adding-related-person/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-64-adding-related-person/StructureDefinition-at-core-practitionerRole.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-practitionerRole</t>
+    <t>https://fhir.hl7.at/core/r5/StructureDefinition/at-core-practitionerRole</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-07T11:38:17+00:00</t>
+    <t>2026-10-13T17:05:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -584,7 +584,7 @@
     <t>PractitionerRole.practitioner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-practitioner)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r5/StructureDefinition/at-core-practitioner)
 </t>
   </si>
   <si>
@@ -600,7 +600,7 @@
     <t>PractitionerRole.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-organization)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r5/StructureDefinition/at-core-organization)
 </t>
   </si>
   <si>
@@ -665,7 +665,7 @@
     <t>Specific specialty associated with the agency.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes|5.0.0</t>
   </si>
   <si>
     <t>PRA-5</t>
@@ -680,7 +680,7 @@
     <t>PractitionerRole.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|5.0.0)
 </t>
   </si>
   <si>
@@ -702,7 +702,7 @@
     <t>PractitionerRole.healthcareService</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(HealthcareService)
+    <t xml:space="preserve">Reference(HealthcareService|5.0.0)
 </t>
   </si>
   <si>
@@ -721,7 +721,7 @@
     <t>PractitionerRole.contact</t>
   </si>
   <si>
-    <t xml:space="preserve">ExtendedContactDetail {http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-extendedContactDetail}
+    <t xml:space="preserve">ExtendedContactDetail {https://fhir.hl7.at/core/r5/StructureDefinition/at-core-extendedContactDetail}
 </t>
   </si>
   <si>
@@ -752,7 +752,7 @@
     <t>A custom attribute that could be provided at a service (e.g. Wheelchair accessibility).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-mode</t>
+    <t>http://hl7.org/fhir/ValueSet/service-mode|5.0.0</t>
   </si>
   <si>
     <t>.actrelationship[typeCode=PERT].observation</t>
@@ -803,7 +803,7 @@
     <t>PractitionerRole.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|5.0.0)
 </t>
   </si>
   <si>
@@ -1140,7 +1140,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="94.0390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="81.37890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r5-core-64-adding-related-person/StructureDefinition-at-core-practitionerRole.xlsx
+++ b/r5-core-64-adding-related-person/StructureDefinition-at-core-practitionerRole.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T17:05:56+00:00</t>
+    <t>2026-10-13T17:36:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
